--- a/deliverables/2026-06-22/scoreboard.xlsx
+++ b/deliverables/2026-06-22/scoreboard.xlsx
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -440,7 +440,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
     <col width="31" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
@@ -830,6 +830,83 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Muster CertCycle (lifecycle + assessor handoff)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Self-serve software + curated assessor handoff (full-cycle subscription)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Regulatory mandate + contractual flow-down (Type 1+2)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5 (Competitive: reach-down; COO: partner dependency)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SERIOUS-BUT-MANAGEABLE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>B (Promising — at A boundary; A-gated on competition)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Not triggered</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Full-cycle CMMC L2 platform: readiness -&gt; audit-ready evidence package -&gt; handoff to an independent partner C3PAO -&gt; recurring stay-certified engine (annual affirmation + prime flow-down auto-answers + 3-yr re-cert); ~$5K-15K/yr + assessor referral fee. Red-team cut competition 7-&gt;6 (FutureFeed already runs the assessor marketplace; durability copyable in 6-12mo), 82.5-&gt;80.7; clears the 80 headline but fails the A-tier competition&gt;=7 gate.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/2026-06-22/scoreboard.xlsx
+++ b/deliverables/2026-06-22/scoreboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -907,6 +907,83 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Muster Managed (AI-leveraged done-with-you MSP)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Managed service (done-with-you) + AI-leveraged human delivery team</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Regulatory mandate + contractual flow-down (Type 1+2)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4 (COO: vendor/partner dependency)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SERIOUS-BUT-MANAGEABLE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>B (Promising)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Not triggered</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Managed 'done-with-you' CMMC L2 service for small DIB shops: automated CUI discovery -&gt; AI-drafted SSP/POA&amp;M/policies -&gt; remediation done via implementation partners -&gt; assessment ownership + warm handoff to an independent C3PAO -&gt; recurring managed continuity; ~$15-40K project + ~$1.5-5K/mo retainer. Red-team cut income/probability/ops 79.2-&gt;76.4; fails A on BOTH the 80 threshold and competition&gt;=7 (Workstreet already markets 'only AI-powered RPO'; Summit 7 reached down to small-biz managed; FutureFeed+Teramis commoditized CUI discovery 2026-06-17). Whole margin rides on the unproven clients-per-FTE ratio.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
